--- a/spreadsheets/domains/cramps-gen_CRAMPS-GEN_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-gen_CRAMPS-GEN_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R96c3ac6f79dc4a42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Rfa75a78ee7794f07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rdd5278bc0e2b4154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Re502857998f24037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="Ra57a17c3ee334a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R534aba32a3464df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rfba41c7cf40f45b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rd38c94279a4b49c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R0f0fcc48278047be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R4c19f94d1b4a4d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R368d11fec1a8404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R595aea35ee67423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rb1b3fca0cd684aec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R2f462e024f244c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="R79e2cf967c6741dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="Re51d0e1d2eb74084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R26a255c8ad4449cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Re7378ebff3a34b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Reaa07ed668354a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R75fd39c9f9a04437"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>population stratification; batch effects; genome-build drift; winner's curse</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
